--- a/research/ibanknet/deliverables/SoCal_SelfUW_Tiered_NoChex_v1.xlsx
+++ b/research/ibanknet/deliverables/SoCal_SelfUW_Tiered_NoChex_v1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="5. CHANGE-COHERENCE LOG" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. SOCAL SELF-UW TIERED'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. SOCAL SELF-UW TIERED'!$A$1:$P$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -106,7 +106,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -161,6 +161,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -234,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -370,6 +375,63 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -736,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -908,6 +970,13 @@
       <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Build date 2026-06-12.  Sources: iBankNet_CA_Deposits_v2, FDIC SOD 6-county census 2025, NCUA 6-county census, deep_chex/secondary_bureaus, deep+rerun bureau, nodoc_dps, chex_socal_cus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA-CORRECTION 2026-06-12: Tier 1 (card-bearing) = NONE. After independent verification, City National &amp; Beneficial State moved to Tier 2 (Chex evidence was absence-only / twin-contaminated, not a confirmed NO); America’s Christian CU &amp; First-Citizens moved to Tier 3 (sources confirm they DO use ChexSystems; lenient=YES). The ONLY strict-verified no-Chex+no-EWS institution is Commercial Bank of California — and it is DEPOSIT-ONLY (no business card). TAKEAWAY: no card-bearing self-UW SoCal bank is verified no-Chex/no-EWS today; the actionable path = Tier 2 (confirm by phone) for the card + a verified no-Chex deposit account (CBC or the fintech layer, Tab 4).</t>
         </is>
       </c>
     </row>
@@ -1026,4115 +1095,4156 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>🟩 TIER 1 — BEST (no Chex / no EWS, verified-absence own-doc)</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="15" t="n"/>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="n"/>
-      <c r="K2" s="15" t="n"/>
-      <c r="L2" s="15" t="n"/>
-      <c r="M2" s="15" t="n"/>
-      <c r="N2" s="15" t="n"/>
-      <c r="O2" s="15" t="n"/>
-      <c r="P2" s="15" t="n"/>
+      <c r="A2" s="50" t="inlineStr">
+        <is>
+          <t>🟩 TIER 1 — BEST: self-UW + card + no-doc + NO Chex + NO EWS + SoCal-confirmed  (verified-clean only)</t>
+        </is>
+      </c>
+      <c r="B2" s="42" t="n"/>
+      <c r="C2" s="42" t="n"/>
+      <c r="D2" s="42" t="n"/>
+      <c r="E2" s="42" t="n"/>
+      <c r="F2" s="42" t="n"/>
+      <c r="G2" s="42" t="n"/>
+      <c r="H2" s="42" t="n"/>
+      <c r="I2" s="42" t="n"/>
+      <c r="J2" s="42" t="n"/>
+      <c r="K2" s="42" t="n"/>
+      <c r="L2" s="42" t="n"/>
+      <c r="M2" s="42" t="n"/>
+      <c r="N2" s="42" t="n"/>
+      <c r="O2" s="42" t="n"/>
+      <c r="P2" s="43" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>🟩 1</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>COMMERCIAL BANK OF CALIFORNIA</t>
+        </is>
+      </c>
+      <c r="C3" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Orange</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>NO (deposit-only)</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t>NO (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>NO (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="L3" s="22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N3" s="22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t>https://cbcal.com</t>
+        </is>
+      </c>
+      <c r="P3" s="22" t="inlineStr">
+        <is>
+          <t>NOTE: Own site has NO issued business-card product (differentiates payment-processing from issuing). Kept in Tier 1 as a deposit-only verified no-Chex/no-EWS option — pair with a Tier-1/2 card from another row.  | https://cbcal.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>🟨 TIER 2 — UNDETERMINED: self-UW + card + SoCal, but Chex/EWS UNKNOWN — confirm by call before applying</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="n"/>
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="42" t="n"/>
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="42" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="42" t="n"/>
+      <c r="N4" s="42" t="n"/>
+      <c r="O4" s="42" t="n"/>
+      <c r="P4" s="43" t="n"/>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>CITY NATIONAL BANK</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Los Angeles, Long Beach, Ontario</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>partial (COMMUNITY-DP)</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>UNK — twin-ambiguous (crediful says uses Chex; CNB-WV twin risk) — verify</t>
+        </is>
+      </c>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>NO (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>Experian — but only from CONSUMER Crystal Visa Infinite myFI (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="22" t="inlineStr">
+        <is>
+          <t>Contact-form/banker</t>
+        </is>
+      </c>
+      <c r="O5" s="22" t="inlineStr">
+        <is>
+          <t>https://www.cnb.com</t>
+        </is>
+      </c>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>https://www.cnb.com/business-banking/lending/credit-cards/commercial.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>BENEFICIAL STATE BANK</t>
+        </is>
+      </c>
+      <c r="C6" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D6" s="57" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E6" s="57" t="inlineStr">
+        <is>
+          <t>Oakland</t>
+        </is>
+      </c>
+      <c r="F6" s="57" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G6" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>beneficialstatebank.com/business-banking (card page 403 on 2026-06-12 — verify live)</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>unknown (none-found)</t>
+        </is>
+      </c>
+      <c r="J6" s="58" t="inlineStr">
+        <is>
+          <t>lean-NO (own-doc absence only — NOT confirmed; verify)</t>
+        </is>
+      </c>
+      <c r="K6" s="59" t="inlineStr">
+        <is>
+          <t>lean-NO (own-doc absence only — verify)</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>No bureau DP; 2 business cards offered but issuer/rail and b (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M6" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>Banker/contact (no online app; primary officer or client team)</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.beneficialstatebank.com</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.beneficialstatebank.com/business-banking/credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>BMO Bank National Association</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="inlineStr">
+        <is>
+          <t>Chicago, Long Beach, Rancho Cucamonga</t>
+        </is>
+      </c>
+      <c r="F7" s="57" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G7" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>partial (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J7" s="58" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K7" s="59" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>TransUnion - BMO business Platinum card cited as a 'pulls Tr</t>
+        </is>
+      </c>
+      <c r="M7" s="57" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bmo.com</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bmo.com/en-us/main/business-banking/credit-cards/platinum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Zions Bancorporation, N.A.</t>
+        </is>
+      </c>
+      <c r="C8" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Long Beach</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K8" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>No new business-specific DP found; myFICO threads (ZIONS BAN (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M8" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N8" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O8" s="22" t="inlineStr">
+        <is>
+          <t>https://www.calbanktrust.com</t>
+        </is>
+      </c>
+      <c r="P8" s="22" t="inlineStr">
+        <is>
+          <t>https://www.calbanktrust.com/business/business-credit-cards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>LOGIX FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Ventura</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K9" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>Experian — membership soft pull = EX; consumer credit card h (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M9" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N9" s="22" t="inlineStr">
+        <is>
+          <t>Appointment (schedule with business banking team; no direct online app)</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t>https://www.logixbanking.com</t>
+        </is>
+      </c>
+      <c r="P9" s="22" t="inlineStr">
+        <is>
+          <t>https://www.logixbanking.com/business/credit-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>SAN DIEGO COUNTY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C10" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Riverside; Orange; San Diego</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>unknown (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>Experian for membership AND credit cards (re-uses membership (B)</t>
+        </is>
+      </c>
+      <c r="M10" s="19" t="inlineStr">
+        <is>
+          <t>$5</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O10" s="22" t="inlineStr">
+        <is>
+          <t>https://www.sdccu.com</t>
+        </is>
+      </c>
+      <c r="P10" s="22" t="inlineStr">
+        <is>
+          <t>https://www.sdccu.com/business/business-credit-card/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>CALIFORNIA FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Orange; San Diego</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Glendale, Long Beach, Fontana, Rancho Cucamonga</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I11" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>UNK (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="K11" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>Experian (consumer-card myFICO DP); no business-card-specifi (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M11" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N11" s="22" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="O11" s="22" t="inlineStr">
+        <is>
+          <t>https://www.ccu.com</t>
+        </is>
+      </c>
+      <c r="P11" s="22" t="inlineStr">
+        <is>
+          <t>https://www.ccu.com/business/loans/business-credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Enterprise Bank &amp; Trust</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Orange; San Diego</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Clayton</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>unknown (none-found)</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>Experian-LEANING via Elan rail — business cards (Smart Busin (RAIL-INFERENCE)</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N12" s="22" t="inlineStr">
+        <is>
+          <t>Contact banker (phone/email/form; no online app)</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t>https://www.enterprisebank.com</t>
+        </is>
+      </c>
+      <c r="P12" s="22" t="inlineStr">
+        <is>
+          <t>https://www.enterprisebank.com/business/credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Washington Federal Bank</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Seattle, Long Beach</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I13" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K13" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>Bureau UNKNOWN; HARD personal-credit underwriting CONFIRMED  (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O13" s="22" t="inlineStr">
+        <is>
+          <t>https://www.wafdbank.com</t>
+        </is>
+      </c>
+      <c r="P13" s="22" t="inlineStr">
+        <is>
+          <t>https://www.wafdbank.com/business-banking/business-credit-cards/small-business-credit-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>St. Louis, Long Beach</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>unknown (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K14" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN bureau — confirmed First Bank uses CorServ Account I (RAIL-INFERENCE)</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O14" s="22" t="inlineStr">
+        <is>
+          <t>https://www.first.bank</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
+        <is>
+          <t>https://www.first.bank/Business/Bank/Business-Credit-Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>PREMIER AMERICA CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Ventura</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Chatsworth</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K15" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>Hard pull confirmed for cards (SuperMoney) but bureau NOT id (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M15" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N15" s="22" t="inlineStr">
+        <is>
+          <t>Online (per prior; site 403 prevented re-check of app flow)</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t>https://www.premieramerica.com</t>
+        </is>
+      </c>
+      <c r="P15" s="22" t="inlineStr">
+        <is>
+          <t>https://www.premieramerica.com/business/loans/premier-business-mastercard</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Sunwest Bank</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Sandy</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I16" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K16" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>NO personal-bureau pull likely. Sunwest Visionary Card = Tor (N/A-BUSINESS-CASHFLOW)</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>Email/contact (VisionaryPayments@SunwestBank.com)</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="inlineStr">
+        <is>
+          <t>https://www.sunwestbank.com</t>
+        </is>
+      </c>
+      <c r="P16" s="22" t="inlineStr">
+        <is>
+          <t>https://www.visionarycorporatecard.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>FIREFIGHTERS FIRST FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I17" s="61" t="inlineStr">
+        <is>
+          <t>NO (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K17" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN bureau — but business Visa card page explicitly conf (Hard (personal credit reviewed per own disclosure))</t>
+        </is>
+      </c>
+      <c r="M17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="22" t="inlineStr">
+        <is>
+          <t>Email/phone (800-231-1626); business membership prereq</t>
+        </is>
+      </c>
+      <c r="O17" s="22" t="inlineStr">
+        <is>
+          <t>https://www.firefightersfirstcu.org</t>
+        </is>
+      </c>
+      <c r="P17" s="22" t="inlineStr">
+        <is>
+          <t>https://www.firefightersfirstcu.org/Business/Business-Loans/Business-Credit-Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>FIRST ENTERTAINMENT CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Hollywood</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I18" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K18" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>Experian-only confirmed across the CU's products (consumer D (B-)</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>https://www.firstent.org</t>
+        </is>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
+        <is>
+          <t>https://www.firstent.org/business/credit-cards/preferred-cash-visa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>HONDA FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Torrance</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>unknown (none-found)</t>
+        </is>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K19" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN — no bureau DP found; note HQ is Marysville OHIO (no (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M19" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
+        <is>
+          <t>https://www.hondafcu.org/</t>
+        </is>
+      </c>
+      <c r="P19" s="22" t="inlineStr">
+        <is>
+          <t>https://www.hondafcu.org/loans-and-credit-cards/credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>UNIVERSITY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C20" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K20" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>Still unknown. University Credit Union (Los Angeles CA, ucu. (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M20" s="19" t="inlineStr">
+        <is>
+          <t>$1</t>
+        </is>
+      </c>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O20" s="22" t="inlineStr">
+        <is>
+          <t>https://www.ucu.org</t>
+        </is>
+      </c>
+      <c r="P20" s="22" t="inlineStr">
+        <is>
+          <t>https://www.ucu.org/banking/business/business-credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>SUN COMMUNITY FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C21" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>El Centro</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>unknown (none-found)</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K21" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN bureau — business credit card exists (cashback 1pt/$ (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M21" s="19" t="inlineStr">
+        <is>
+          <t>$1</t>
+        </is>
+      </c>
+      <c r="N21" s="22" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="O21" s="22" t="inlineStr">
+        <is>
+          <t>https://www.suncommunity.com</t>
+        </is>
+      </c>
+      <c r="P21" s="22" t="inlineStr">
+        <is>
+          <t>https://www.suncommunity.com/products/business-credit-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>USC CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C22" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>unknown (none-found)</t>
+        </is>
+      </c>
+      <c r="J22" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K22" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>Still unknown. USC Credit Union (Los Angeles CA) offers Mast (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M22" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>https://www.usccreditunion.org</t>
+        </is>
+      </c>
+      <c r="P22" s="22" t="inlineStr">
+        <is>
+          <t>https://www.usccreditunion.org/business-banking/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Shinhan Bank America</t>
+        </is>
+      </c>
+      <c r="C23" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Orange; San Diego</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I23" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K23" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>No bureau DP; relationship-based business card (deposit/loan (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M23" s="19" t="inlineStr">
+        <is>
+          <t>$4000</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="O23" s="22" t="inlineStr">
+        <is>
+          <t>https://www.shbamerica.com</t>
+        </is>
+      </c>
+      <c r="P23" s="22" t="inlineStr">
+        <is>
+          <t>https://www.shbamerica.com/business-business-credit-card/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>INTERFAITH FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C24" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Montclair</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I24" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J24" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K24" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>Still unknown. Interfaith FCU (Montclair CA; ~$121M, ~6K mem (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M24" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="inlineStr">
+        <is>
+          <t>https://interfaithfcu.org</t>
+        </is>
+      </c>
+      <c r="P24" s="22" t="inlineStr">
+        <is>
+          <t>https://interfaithfcu.org/business-visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>CALIFORNIA COMMUNITY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Orange; San Diego</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J25" s="31" t="inlineStr">
+        <is>
+          <t>UNK (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="K25" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>NO BUSINESS CARD — CACCU offers ONLY consumer Visa Platinum  (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M25" s="19" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="N25" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O25" s="22" t="inlineStr">
+        <is>
+          <t>https://www.caccu.org</t>
+        </is>
+      </c>
+      <c r="P25" s="22" t="inlineStr">
+        <is>
+          <t>https://www.caccu.org/loans/visa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>WEST COAST COMMUNITY BANK</t>
+        </is>
+      </c>
+      <c r="C26" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Ventura</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J26" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K26" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>Cards issued/serviced by TCM Bank, N.A. (rail). TCM hard-pul (RAIL-INFERENCE)</t>
+        </is>
+      </c>
+      <c r="M26" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>Phone/RM (Corporate Card Mgr 831.457.5000; no online app)</t>
+        </is>
+      </c>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>https://wccb.com</t>
+        </is>
+      </c>
+      <c r="P26" s="22" t="inlineStr">
+        <is>
+          <t>https://wccb.com/corporate_cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>MONTECITO BANK &amp; TRUST</t>
+        </is>
+      </c>
+      <c r="C27" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Ventura</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Santa Barbara</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>NO (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="K27" s="30" t="inlineStr">
+        <is>
+          <t>UNK (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN — issuer not confirmed on public pages; uses SpendTr (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M27" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N27" s="22" t="inlineStr">
+        <is>
+          <t>Assisted (appointment/banker)</t>
+        </is>
+      </c>
+      <c r="O27" s="22" t="inlineStr">
+        <is>
+          <t>https://montecito.bank</t>
+        </is>
+      </c>
+      <c r="P27" s="22" t="inlineStr">
+        <is>
+          <t>https://montecito.bank/business/credit-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>🟨 2</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>VENTURA COUNTY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C28" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Ventura</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Ventura</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J28" s="31" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="K28" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN bureau — VCCU offers business Visa; no membership or (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M28" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="22" t="inlineStr">
+        <is>
+          <t>Branch/phone</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="inlineStr">
+        <is>
+          <t>https://www.vccuonline.net</t>
+        </is>
+      </c>
+      <c r="P28" s="22" t="inlineStr">
+        <is>
+          <t>https://www.vccuonline.net/Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>🟥 TIER 3 — SCREENS: pulls ChexSystems and/or EWS (confirmed) — sequence early/with clean file or skip</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="42" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="42" t="n"/>
+      <c r="G29" s="42" t="n"/>
+      <c r="H29" s="42" t="n"/>
+      <c r="I29" s="42" t="n"/>
+      <c r="J29" s="42" t="n"/>
+      <c r="K29" s="42" t="n"/>
+      <c r="L29" s="42" t="n"/>
+      <c r="M29" s="42" t="n"/>
+      <c r="N29" s="42" t="n"/>
+      <c r="O29" s="42" t="n"/>
+      <c r="P29" s="43" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>First-Citizens Bank &amp; Trust Company</t>
+        </is>
+      </c>
+      <c r="C30" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Raleigh, Long Beach</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J30" s="37" t="inlineStr">
+        <is>
+          <t>YES (uses ChexSystems — DoC/own disclosure)</t>
+        </is>
+      </c>
+      <c r="K30" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>Mixed/all-three reported (single DP: pulls all 3 personal +  (COMMUNITY-DP (single thread; tri-pull claim from search snippet - verify in thread))</t>
+        </is>
+      </c>
+      <c r="M30" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N30" s="22" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="O30" s="22" t="inlineStr">
+        <is>
+          <t>https://www.firstcitizens.com</t>
+        </is>
+      </c>
+      <c r="P30" s="22" t="inlineStr">
+        <is>
+          <t>https://www.firstcitizens.com/small-business/credit-financing/credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B31" s="37" t="inlineStr">
+        <is>
+          <t>AMERICA'S CHRISTIAN CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C31" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Glendora</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J31" s="37" t="inlineStr">
+        <is>
+          <t>YES — lenient (DOES use ChexSystems; Unchex)</t>
+        </is>
+      </c>
+      <c r="K31" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L31" s="22" t="inlineStr">
+        <is>
+          <t>No bureau DP; Visa Business/Ministry Rewards card exists, 'S (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M31" s="19" t="inlineStr">
+        <is>
+          <t>$3500</t>
+        </is>
+      </c>
+      <c r="N31" s="22" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="O31" s="22" t="inlineStr">
+        <is>
+          <t>https://americaschristiancu.com/</t>
+        </is>
+      </c>
+      <c r="P31" s="22" t="inlineStr">
+        <is>
+          <t>https://americaschristiancu.com/organization/visa-business-rewards-credit-card/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>Bank of America, National Association</t>
+        </is>
+      </c>
+      <c r="C32" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D32" s="57" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E32" s="57" t="inlineStr">
+        <is>
+          <t>Charlotte, Long Beach</t>
+        </is>
+      </c>
+      <c r="F32" s="57" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G32" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J32" s="65" t="inlineStr">
         <is>
           <t>NO (COMMUNITY-DP)</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K32" s="63" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="L32" s="57" t="inlineStr">
+        <is>
+          <t>EX usual; CA mixed (EX/TU/EQ) — no business-specific upgrade (COMMUNITY-DP-business)</t>
+        </is>
+      </c>
+      <c r="M32" s="57" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>https://business.bankofamerica.com</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>https://business.bankofamerica.com/en/credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="66" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>Wells Fargo Bank, National Association</t>
+        </is>
+      </c>
+      <c r="C33" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D33" s="57" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E33" s="57" t="inlineStr">
+        <is>
+          <t>Sioux Falls, Long Beach, Fontana</t>
+        </is>
+      </c>
+      <c r="F33" s="57" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G33" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J33" s="64" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K33" s="63" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>Experian dominant for the Signify Business Cash/Business car (B)</t>
+        </is>
+      </c>
+      <c r="M33" s="57" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>Online (also branch by appt)</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.wellsfargo.com</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t>https://www.wellsfargo.com/biz/business-credit/credit-cards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Bank, National Association</t>
+        </is>
+      </c>
+      <c r="C34" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Columbus, Long Beach, Fontana</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>NO (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K34" s="36" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="L34" s="22" t="inlineStr">
+        <is>
+          <t>Experian dominant in CA (~70%+ of Chase pulls nationally; CA (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="M34" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N34" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O34" s="22" t="inlineStr">
+        <is>
+          <t>https://www.chase.com</t>
+        </is>
+      </c>
+      <c r="P34" s="22" t="inlineStr">
+        <is>
+          <t>https://creditcards.chase.com/business-credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association</t>
+        </is>
+      </c>
+      <c r="C35" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Cincinnati, Long Beach, Fontana, Wilmington</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J35" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K35" s="36" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="L35" s="22" t="inlineStr">
+        <is>
+          <t>TU-usual for business (CA consumer: TU 47%/EX 26%/EQ 5%) (COMMUNITY-DP (business-specific myFICO DPs))</t>
+        </is>
+      </c>
+      <c r="M35" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N35" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O35" s="22" t="inlineStr">
+        <is>
+          <t>https://www.usbank.com</t>
+        </is>
+      </c>
+      <c r="P35" s="22" t="inlineStr">
+        <is>
+          <t>https://www.usbank.com/business-banking/business-credit-cards.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>Citibank, National Association</t>
+        </is>
+      </c>
+      <c r="C36" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Sioux Falls, Long Beach, Fontana</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J36" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K36" s="36" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
+        <is>
+          <t>Experian primary for Citi AAdvantage Business card; Citi BUS (B)</t>
+        </is>
+      </c>
+      <c r="M36" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N36" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O36" s="22" t="inlineStr">
+        <is>
+          <t>https://www.citi.com</t>
+        </is>
+      </c>
+      <c r="P36" s="22" t="inlineStr">
+        <is>
+          <t>https://www.citi.com/credit-cards/compare/business-credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>Western Alliance Bank</t>
+        </is>
+      </c>
+      <c r="C37" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Diego</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I37" s="61" t="inlineStr">
+        <is>
+          <t>unknown (UNVERIFIED-RUMOR)</t>
+        </is>
+      </c>
+      <c r="J37" s="37" t="inlineStr">
+        <is>
+          <t>YES (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="inlineStr">
         <is>
           <t>NO (VERIFIED-own-doc)</t>
         </is>
       </c>
-      <c r="L3" s="22" t="inlineStr">
-        <is>
-          <t>Experian — but only from CONSUMER Crystal Visa Infinite myFI (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M3" s="20" t="inlineStr">
+      <c r="L37" s="22" t="inlineStr">
+        <is>
+          <t>Business Plus Visa card issued DIRECTLY by Western Alliance  (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M37" s="19" t="inlineStr">
+        <is>
+          <t>$1,</t>
+        </is>
+      </c>
+      <c r="N37" s="22" t="inlineStr">
+        <is>
+          <t>Online form -&gt; banker callback in 2-3 business days (not instant online decision)</t>
+        </is>
+      </c>
+      <c r="O37" s="22" t="inlineStr">
+        <is>
+          <t>https://www.westernalliancebancorporation.com</t>
+        </is>
+      </c>
+      <c r="P37" s="22" t="inlineStr">
+        <is>
+          <t>https://www.westernalliancebancorporation.com/small-business/credit-cards/business-plus-credit-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>PNC Bank, National Association</t>
+        </is>
+      </c>
+      <c r="C38" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; San Diego</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J38" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K38" s="36" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="L38" s="22" t="inlineStr">
+        <is>
+          <t>Experian-leaning for PNC Visa Business per WalletHub + Credi</t>
+        </is>
+      </c>
+      <c r="M38" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N38" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O38" s="22" t="inlineStr">
+        <is>
+          <t>https://www.pnc.com</t>
+        </is>
+      </c>
+      <c r="P38" s="22" t="inlineStr">
+        <is>
+          <t>https://www.pnc.com/en/small-business/borrowing/business-credit-cards/pnc-visa-business-credit-card.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>KINECTA FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C39" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Orange; Ventura</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Manhattan Beach</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>partial (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J39" s="37" t="inlineStr">
+        <is>
+          <t>YES (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="K39" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L39" s="22" t="inlineStr">
+        <is>
+          <t>No business-card-specific DP; myFICO 'I'm Embarrassed 2nd Pe (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M39" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N39" s="22" t="inlineStr">
+        <is>
+          <t>In-person/phone (book appointment or 800.854.9846; no online app)</t>
+        </is>
+      </c>
+      <c r="O39" s="22" t="inlineStr">
+        <is>
+          <t>https://www.kinecta.org</t>
+        </is>
+      </c>
+      <c r="P39" s="22" t="inlineStr">
+        <is>
+          <t>https://www.kinecta.org/credit-card/mypro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>NUVISION FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C40" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; Orange; San Diego</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Huntington Beac, Carson</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I40" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J40" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K40" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L40" s="22" t="inlineStr">
+        <is>
+          <t>Still unknown. NuVision (Huntington Beach CA; Denali AK divi (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M40" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N40" s="22" t="inlineStr">
+        <is>
+          <t>Online (also fax/branch form)</t>
+        </is>
+      </c>
+      <c r="O40" s="22" t="inlineStr">
+        <is>
+          <t>https://nuvisionfederal.com</t>
+        </is>
+      </c>
+      <c r="P40" s="22" t="inlineStr">
+        <is>
+          <t>https://nuvisionfederal.com/business-banking/credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>PROVIDENT CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>San Bernardino; Riverside</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I41" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J41" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K41" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L41" s="22" t="inlineStr">
+        <is>
+          <t>Hard pull CONFIRMED for cards (SuperMoney); bureau NOT ident (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M41" s="19" t="inlineStr">
+        <is>
+          <t>$1</t>
+        </is>
+      </c>
+      <c r="N41" s="22" t="inlineStr">
+        <is>
+          <t>Online (member flow: new members open biz savings first; existing via online banking)</t>
+        </is>
+      </c>
+      <c r="O41" s="22" t="inlineStr">
+        <is>
+          <t>https://www.providentcu.org</t>
+        </is>
+      </c>
+      <c r="P41" s="22" t="inlineStr">
+        <is>
+          <t>https://www.providentcu.org/business/business-credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>Banner Bank</t>
+        </is>
+      </c>
+      <c r="C42" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Riverside; San Diego</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Walla Walla, Rancho Cucamonga</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I42" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J42" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K42" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L42" s="22" t="inlineStr">
+        <is>
+          <t>CONFIRMED self-issued: Banner Bank Business Mastercard Credi (VERIFIED-DISCLOSURE)</t>
+        </is>
+      </c>
+      <c r="M42" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N42" s="22" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="O42" s="22" t="inlineStr">
+        <is>
+          <t>https://www.bannerbank.com</t>
+        </is>
+      </c>
+      <c r="P42" s="22" t="inlineStr">
+        <is>
+          <t>https://www.bannerbank.com/business-solutions/services/small-business-credit-card/business-platinum-mastercard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>ORANGE COUNTY'S FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C43" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Bernardino; Orange</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Santa Ana, Long Beach</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>unknown (none-found)</t>
+        </is>
+      </c>
+      <c r="J43" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K43" s="36" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="L43" s="22" t="inlineStr">
+        <is>
+          <t>EXPERIAN - own FAQ/knowledge base states: 'typically pulls a</t>
+        </is>
+      </c>
+      <c r="M43" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N43" s="22" t="inlineStr">
+        <is>
+          <t>Branch/phone (no online business-card app found)</t>
+        </is>
+      </c>
+      <c r="O43" s="22" t="inlineStr">
+        <is>
+          <t>https://www.orangecountyscu.org</t>
+        </is>
+      </c>
+      <c r="P43" s="22" t="inlineStr">
+        <is>
+          <t>https://www.orangecountyscu.org/products/business-services/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>ALTURA FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C44" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I44" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J44" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K44" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr">
+        <is>
+          <t>No business-card-specific DP. Altura credit-reporting-agenci (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M44" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N44" s="22" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="O44" s="22" t="inlineStr">
+        <is>
+          <t>https://www.alturacu.com</t>
+        </is>
+      </c>
+      <c r="P44" s="22" t="inlineStr">
+        <is>
+          <t>https://www.alturacu.com/business-credit-card/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>MidFirst Bank</t>
+        </is>
+      </c>
+      <c r="C45" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Diego</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>⭐ YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J45" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K45" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L45" s="22" t="inlineStr">
+        <is>
+          <t>Mixed/any of three — WalletHub answer is consumer-card gener (CONSUMER-PROXY)</t>
+        </is>
+      </c>
+      <c r="M45" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N3" s="22" t="inlineStr">
-        <is>
-          <t>Contact-form/banker</t>
-        </is>
-      </c>
-      <c r="O3" s="22" t="inlineStr">
-        <is>
-          <t>https://www.cnb.com</t>
-        </is>
-      </c>
-      <c r="P3" s="22" t="inlineStr">
-        <is>
-          <t>https://www.cnb.com/business-banking/lending/credit-cards/commercial.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>🟩 1</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>COMMERCIAL BANK OF CALIFORNIA</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="N45" s="22" t="inlineStr">
+        <is>
+          <t>In-person (banking center / local banker; no online app shown)</t>
+        </is>
+      </c>
+      <c r="O45" s="22" t="inlineStr">
+        <is>
+          <t>https://www.midfirst.com</t>
+        </is>
+      </c>
+      <c r="P45" s="22" t="inlineStr">
+        <is>
+          <t>https://www.midfirst.com/business-and-commercial/card-solutions/credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>Valley National Bank</t>
+        </is>
+      </c>
+      <c r="C46" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>Passaic</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J46" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K46" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L46" s="22" t="inlineStr">
+        <is>
+          <t>Inquiry bureau still unknown. Confirmed product = Valley Vis (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M46" s="19" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="N46" s="22" t="inlineStr">
+        <is>
+          <t>Interest form online then rep contact (no direct online app)</t>
+        </is>
+      </c>
+      <c r="O46" s="22" t="inlineStr">
+        <is>
+          <t>https://www.valley.com</t>
+        </is>
+      </c>
+      <c r="P46" s="22" t="inlineStr">
+        <is>
+          <t>https://www.valley.com/business/commercial-lending/valley-visa-business-credit-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>BAY FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C47" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Redondo Beach</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I47" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J47" s="37" t="inlineStr">
+        <is>
+          <t>YES (VERIFIED-own-doc)</t>
+        </is>
+      </c>
+      <c r="K47" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L47" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN bureau — Business Visa card exists (in-house CU card (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M47" s="19" t="inlineStr">
+        <is>
+          <t>$50K</t>
+        </is>
+      </c>
+      <c r="N47" s="19" t="inlineStr">
+        <is>
+          <t>Contact/branch</t>
+        </is>
+      </c>
+      <c r="O47" s="22" t="inlineStr">
+        <is>
+          <t>https://www.bayfed.com</t>
+        </is>
+      </c>
+      <c r="P47" s="22" t="inlineStr">
+        <is>
+          <t>https://www.bayfed.com/business/visa-credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>CHRISTIAN COMMUNITY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C48" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>Los Angeles; Orange</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>San Dimas</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I48" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J48" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K48" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L48" s="22" t="inlineStr">
+        <is>
+          <t>No bureau DP; now operates as AdelFi; business Visa Rewards  (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M48" s="19" t="inlineStr">
+        <is>
+          <t>$300</t>
+        </is>
+      </c>
+      <c r="N48" s="22" t="inlineStr">
+        <is>
+          <t>Contact/assisted ('Contact Us to Apply'; AdelFi membership required first)</t>
+        </is>
+      </c>
+      <c r="O48" s="22" t="inlineStr">
+        <is>
+          <t>https://www.adelfibanking.com</t>
+        </is>
+      </c>
+      <c r="P48" s="22" t="inlineStr">
+        <is>
+          <t>https://www.adelfibanking.com/ministry/ministry-credit-cards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>LOS ANGELES FEDERAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C49" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I49" s="22" t="inlineStr">
+        <is>
+          <t>unknown (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="J49" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K49" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L49" s="22" t="inlineStr">
+        <is>
+          <t>TransUnion primary — myFICO DPs: membership hard pull hits T (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="M49" s="19" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="N49" s="22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="O49" s="22" t="inlineStr">
+        <is>
+          <t>https://www.lafcu.org</t>
+        </is>
+      </c>
+      <c r="P49" s="22" t="inlineStr">
+        <is>
+          <t>https://www.lafcu.org/loans-credit/business-loans</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>Sunflower Bank, National Association</t>
+        </is>
+      </c>
+      <c r="C50" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>Los Angeles; San Diego</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G50" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I50" s="22" t="inlineStr">
+        <is>
+          <t>unknown (-)</t>
+        </is>
+      </c>
+      <c r="J50" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K50" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L50" s="22" t="inlineStr">
+        <is>
+          <t>UNKNOWN — Sunflower self-issues business cards (Visa, licens (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M50" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>NO (deposit-only)</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t>NO (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="K4" s="24" t="inlineStr">
-        <is>
-          <t>NO (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M4" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O4" s="22" t="inlineStr">
-        <is>
-          <t>https://cbcal.com</t>
-        </is>
-      </c>
-      <c r="P4" s="25" t="inlineStr">
-        <is>
-          <t>NOTE: Own site has NO issued business-card product (differentiates payment-processing from issuing). Kept in Tier 1 as a deposit-only verified no-Chex/no-EWS option — pair with a Tier-1/2 card from another row.  | https://cbcal.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>🟩 1</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>BENEFICIAL STATE BANK</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>Oakland</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="N50" s="22" t="inlineStr">
+        <is>
+          <t>Branch/contact (no online app found)</t>
+        </is>
+      </c>
+      <c r="O50" s="22" t="inlineStr">
+        <is>
+          <t>https://www.sunflowerbank.com</t>
+        </is>
+      </c>
+      <c r="P50" s="22" t="inlineStr">
+        <is>
+          <t>https://www.sunflowerbank.com/business/business-accounts/credit-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="62" t="inlineStr">
+        <is>
+          <t>🟥 3</t>
+        </is>
+      </c>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>SIERRA CENTRAL CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C51" s="52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Ventura</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Porterville</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
-        <is>
-          <t>unknown (none-found)</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="inlineStr">
-        <is>
-          <t>NO (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="K5" s="24" t="inlineStr">
-        <is>
-          <t>NO (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t>No bureau DP; 2 business cards offered but issuer/rail and b (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M5" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="22" t="inlineStr">
-        <is>
-          <t>Banker/contact (no online app; primary officer or client team)</t>
-        </is>
-      </c>
-      <c r="O5" s="22" t="inlineStr">
-        <is>
-          <t>https://www.beneficialstatebank.com</t>
-        </is>
-      </c>
-      <c r="P5" s="22" t="inlineStr">
-        <is>
-          <t>https://www.beneficialstatebank.com/business-banking/credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>🟨 TIER 2 — UNDETERMINED (Chex or EWS unknown)</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>First-Citizens Bank &amp; Trust Company</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>Raleigh, Long Beach</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I8" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>NO (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K8" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t>Mixed/all-three reported (single DP: pulls all 3 personal +  (COMMUNITY-DP (single thread; tri-pull claim from search snippet - verify in thread))</t>
-        </is>
-      </c>
-      <c r="M8" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N8" s="22" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="O8" s="22" t="inlineStr">
-        <is>
-          <t>https://www.firstcitizens.com</t>
-        </is>
-      </c>
-      <c r="P8" s="22" t="inlineStr">
-        <is>
-          <t>https://www.firstcitizens.com/small-business/credit-financing/credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>BMO Bank National Association</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>Chicago, Long Beach, Rancho Cucamonga</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>partial (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J9" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L9" s="22" t="inlineStr">
-        <is>
-          <t>TransUnion - BMO business Platinum card cited as a 'pulls Tr</t>
-        </is>
-      </c>
-      <c r="M9" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="I51" s="61" t="inlineStr">
+        <is>
+          <t>⭐ YES (VERIFIED-own-page)</t>
+        </is>
+      </c>
+      <c r="J51" s="37" t="inlineStr">
+        <is>
+          <t>YES (COMMUNITY-DP)</t>
+        </is>
+      </c>
+      <c r="K51" s="30" t="inlineStr">
+        <is>
+          <t>UNK</t>
+        </is>
+      </c>
+      <c r="L51" s="22" t="inlineStr">
+        <is>
+          <t>Still unknown. Sierra Central (Yuba City CA) offers a self-b (UNKNOWN)</t>
+        </is>
+      </c>
+      <c r="M51" s="19" t="inlineStr">
+        <is>
+          <t>$5K</t>
+        </is>
+      </c>
+      <c r="N51" s="22" t="inlineStr">
         <is>
           <t>Online</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
-        <is>
-          <t>https://www.bmo.com</t>
-        </is>
-      </c>
-      <c r="P9" s="22" t="inlineStr">
-        <is>
-          <t>https://www.bmo.com/en-us/main/business-banking/credit-cards/platinum/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>Zions Bancorporation, N.A.</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>Salt Lake City, Long Beach</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I10" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J10" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K10" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>No new business-specific DP found; myFICO threads (ZIONS BAN (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N10" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O10" s="22" t="inlineStr">
-        <is>
-          <t>https://www.calbanktrust.com</t>
-        </is>
-      </c>
-      <c r="P10" s="22" t="inlineStr">
-        <is>
-          <t>https://www.calbanktrust.com/business/business-credit-cards/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>LOGIX FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Ventura</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J11" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K11" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L11" s="22" t="inlineStr">
-        <is>
-          <t>Experian — membership soft pull = EX; consumer credit card h (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N11" s="22" t="inlineStr">
-        <is>
-          <t>Appointment (schedule with business banking team; no direct online app)</t>
-        </is>
-      </c>
-      <c r="O11" s="22" t="inlineStr">
-        <is>
-          <t>https://www.logixbanking.com</t>
-        </is>
-      </c>
-      <c r="P11" s="22" t="inlineStr">
-        <is>
-          <t>https://www.logixbanking.com/business/credit-card</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>SAN DIEGO COUNTY CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>Riverside; Orange; San Diego</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>unknown (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J12" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K12" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L12" s="22" t="inlineStr">
-        <is>
-          <t>Experian for membership AND credit cards (re-uses membership (B)</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="inlineStr">
-        <is>
-          <t>$5</t>
-        </is>
-      </c>
-      <c r="N12" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O12" s="22" t="inlineStr">
-        <is>
-          <t>https://www.sdccu.com</t>
-        </is>
-      </c>
-      <c r="P12" s="22" t="inlineStr">
-        <is>
-          <t>https://www.sdccu.com/business/business-credit-card/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>CALIFORNIA FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Orange; San Diego</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>Glendale, Long Beach, Fontana, Rancho Cucamonga</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I13" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J13" s="31" t="inlineStr">
-        <is>
-          <t>UNK (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="K13" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L13" s="22" t="inlineStr">
-        <is>
-          <t>Experian (consumer-card myFICO DP); no business-card-specifi (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M13" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="O13" s="22" t="inlineStr">
-        <is>
-          <t>https://www.ccu.com</t>
-        </is>
-      </c>
-      <c r="P13" s="22" t="inlineStr">
-        <is>
-          <t>https://www.ccu.com/business/loans/business-credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Enterprise Bank &amp; Trust</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Orange; San Diego</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>Clayton</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>unknown (none-found)</t>
-        </is>
-      </c>
-      <c r="J14" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K14" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="inlineStr">
-        <is>
-          <t>Experian-LEANING via Elan rail — business cards (Smart Busin (RAIL-INFERENCE)</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>Contact banker (phone/email/form; no online app)</t>
-        </is>
-      </c>
-      <c r="O14" s="22" t="inlineStr">
-        <is>
-          <t>https://www.enterprisebank.com</t>
-        </is>
-      </c>
-      <c r="P14" s="22" t="inlineStr">
-        <is>
-          <t>https://www.enterprisebank.com/business/credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Washington Federal Bank</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>Seattle, Long Beach</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K15" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="inlineStr">
-        <is>
-          <t>Bureau UNKNOWN; HARD personal-credit underwriting CONFIRMED  (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="O15" s="22" t="inlineStr">
-        <is>
-          <t>https://www.wafdbank.com</t>
-        </is>
-      </c>
-      <c r="P15" s="22" t="inlineStr">
-        <is>
-          <t>https://www.wafdbank.com/business-banking/business-credit-cards/small-business-credit-card</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>St. Louis, Long Beach</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>unknown (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K16" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L16" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN bureau — confirmed First Bank uses CorServ Account I (RAIL-INFERENCE)</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O16" s="22" t="inlineStr">
-        <is>
-          <t>https://www.first.bank</t>
-        </is>
-      </c>
-      <c r="P16" s="22" t="inlineStr">
-        <is>
-          <t>https://www.first.bank/Business/Bank/Business-Credit-Cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>PREMIER AMERICA CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Ventura</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>Chatsworth</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J17" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K17" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="inlineStr">
-        <is>
-          <t>Hard pull confirmed for cards (SuperMoney) but bureau NOT id (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N17" s="22" t="inlineStr">
-        <is>
-          <t>Online (per prior; site 403 prevented re-check of app flow)</t>
-        </is>
-      </c>
-      <c r="O17" s="22" t="inlineStr">
-        <is>
-          <t>https://www.premieramerica.com</t>
-        </is>
-      </c>
-      <c r="P17" s="22" t="inlineStr">
-        <is>
-          <t>https://www.premieramerica.com/business/loans/premier-business-mastercard</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>Sunwest Bank</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>Sandy</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J18" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K18" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>NO personal-bureau pull likely. Sunwest Visionary Card = Tor (N/A-BUSINESS-CASHFLOW)</t>
-        </is>
-      </c>
-      <c r="M18" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
-        <is>
-          <t>Email/contact (VisionaryPayments@SunwestBank.com)</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>https://www.sunwestbank.com</t>
-        </is>
-      </c>
-      <c r="P18" s="22" t="inlineStr">
-        <is>
-          <t>https://www.visionarycorporatecard.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>FIREFIGHTERS FIRST FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>NO (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J19" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K19" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN bureau — but business Visa card page explicitly conf (Hard (personal credit reviewed per own disclosure))</t>
-        </is>
-      </c>
-      <c r="M19" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="22" t="inlineStr">
-        <is>
-          <t>Email/phone (800-231-1626); business membership prereq</t>
-        </is>
-      </c>
-      <c r="O19" s="22" t="inlineStr">
-        <is>
-          <t>https://www.firefightersfirstcu.org</t>
-        </is>
-      </c>
-      <c r="P19" s="22" t="inlineStr">
-        <is>
-          <t>https://www.firefightersfirstcu.org/Business/Business-Loans/Business-Credit-Cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>FIRST ENTERTAINMENT CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>Hollywood</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J20" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K20" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="inlineStr">
-        <is>
-          <t>Experian-only confirmed across the CU's products (consumer D (B-)</t>
-        </is>
-      </c>
-      <c r="M20" s="20" t="inlineStr">
-        <is>
-          <t>$100</t>
-        </is>
-      </c>
-      <c r="N20" s="19" t="inlineStr">
-        <is>
-          <t>Call</t>
-        </is>
-      </c>
-      <c r="O20" s="22" t="inlineStr">
-        <is>
-          <t>https://www.firstent.org</t>
-        </is>
-      </c>
-      <c r="P20" s="22" t="inlineStr">
-        <is>
-          <t>https://www.firstent.org/business/credit-cards/preferred-cash-visa/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>HONDA FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>Torrance</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>unknown (none-found)</t>
-        </is>
-      </c>
-      <c r="J21" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K21" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L21" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN — no bureau DP found; note HQ is Marysville OHIO (no (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M21" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="O21" s="22" t="inlineStr">
-        <is>
-          <t>https://www.hondafcu.org/</t>
-        </is>
-      </c>
-      <c r="P21" s="22" t="inlineStr">
-        <is>
-          <t>https://www.hondafcu.org/loans-and-credit-cards/credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>UNIVERSITY CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J22" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K22" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L22" s="22" t="inlineStr">
-        <is>
-          <t>Still unknown. University Credit Union (Los Angeles CA, ucu. (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M22" s="20" t="inlineStr">
-        <is>
-          <t>$1</t>
-        </is>
-      </c>
-      <c r="N22" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O22" s="22" t="inlineStr">
-        <is>
-          <t>https://www.ucu.org</t>
-        </is>
-      </c>
-      <c r="P22" s="22" t="inlineStr">
-        <is>
-          <t>https://www.ucu.org/banking/business/business-credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>SUN COMMUNITY FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>El Centro</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>unknown (none-found)</t>
-        </is>
-      </c>
-      <c r="J23" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K23" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN bureau — business credit card exists (cashback 1pt/$ (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M23" s="20" t="inlineStr">
-        <is>
-          <t>$1</t>
-        </is>
-      </c>
-      <c r="N23" s="19" t="inlineStr">
-        <is>
-          <t>Call</t>
-        </is>
-      </c>
-      <c r="O23" s="22" t="inlineStr">
-        <is>
-          <t>https://www.suncommunity.com</t>
-        </is>
-      </c>
-      <c r="P23" s="22" t="inlineStr">
-        <is>
-          <t>https://www.suncommunity.com/products/business-credit-card</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B24" s="29" t="inlineStr">
-        <is>
-          <t>AMERICA'S CHRISTIAN CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>Glendora</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t>NO (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K24" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="inlineStr">
-        <is>
-          <t>No bureau DP; Visa Business/Ministry Rewards card exists, 'S (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M24" s="20" t="inlineStr">
-        <is>
-          <t>$3500</t>
-        </is>
-      </c>
-      <c r="N24" s="22" t="inlineStr">
-        <is>
-          <t>Call</t>
-        </is>
-      </c>
-      <c r="O24" s="22" t="inlineStr">
-        <is>
-          <t>https://americaschristiancu.com/</t>
-        </is>
-      </c>
-      <c r="P24" s="22" t="inlineStr">
-        <is>
-          <t>https://americaschristiancu.com/organization/visa-business-rewards-credit-card/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>USC CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>unknown (none-found)</t>
-        </is>
-      </c>
-      <c r="J25" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K25" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L25" s="22" t="inlineStr">
-        <is>
-          <t>Still unknown. USC Credit Union (Los Angeles CA) offers Mast (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O25" s="22" t="inlineStr">
-        <is>
-          <t>https://www.usccreditunion.org</t>
-        </is>
-      </c>
-      <c r="P25" s="22" t="inlineStr">
-        <is>
-          <t>https://www.usccreditunion.org/business-banking/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B26" s="29" t="inlineStr">
-        <is>
-          <t>Shinhan Bank America</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Orange; San Diego</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I26" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J26" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K26" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L26" s="22" t="inlineStr">
-        <is>
-          <t>No bureau DP; relationship-based business card (deposit/loan (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M26" s="20" t="inlineStr">
-        <is>
-          <t>$4000</t>
-        </is>
-      </c>
-      <c r="N26" s="22" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="O26" s="22" t="inlineStr">
-        <is>
-          <t>https://www.shbamerica.com</t>
-        </is>
-      </c>
-      <c r="P26" s="22" t="inlineStr">
-        <is>
-          <t>https://www.shbamerica.com/business-business-credit-card/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B27" s="29" t="inlineStr">
-        <is>
-          <t>INTERFAITH FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>San Bernardino</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>Montclair</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I27" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J27" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K27" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L27" s="22" t="inlineStr">
-        <is>
-          <t>Still unknown. Interfaith FCU (Montclair CA; ~$121M, ~6K mem (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M27" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N27" s="19" t="inlineStr">
-        <is>
-          <t>Call</t>
-        </is>
-      </c>
-      <c r="O27" s="22" t="inlineStr">
-        <is>
-          <t>https://interfaithfcu.org</t>
-        </is>
-      </c>
-      <c r="P27" s="22" t="inlineStr">
-        <is>
-          <t>https://interfaithfcu.org/business-visa</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B28" s="29" t="inlineStr">
-        <is>
-          <t>CALIFORNIA COMMUNITY CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Orange; San Diego</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J28" s="31" t="inlineStr">
-        <is>
-          <t>UNK (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="K28" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L28" s="22" t="inlineStr">
-        <is>
-          <t>NO BUSINESS CARD — CACCU offers ONLY consumer Visa Platinum  (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M28" s="20" t="inlineStr">
-        <is>
-          <t>$500</t>
-        </is>
-      </c>
-      <c r="N28" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="O28" s="22" t="inlineStr">
-        <is>
-          <t>https://www.caccu.org</t>
-        </is>
-      </c>
-      <c r="P28" s="22" t="inlineStr">
-        <is>
-          <t>https://www.caccu.org/loans/visa/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="inlineStr">
-        <is>
-          <t>WEST COAST COMMUNITY BANK</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>Ventura</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>Fresno</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J29" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K29" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L29" s="22" t="inlineStr">
-        <is>
-          <t>Cards issued/serviced by TCM Bank, N.A. (rail). TCM hard-pul (RAIL-INFERENCE)</t>
-        </is>
-      </c>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N29" s="22" t="inlineStr">
-        <is>
-          <t>Phone/RM (Corporate Card Mgr 831.457.5000; no online app)</t>
-        </is>
-      </c>
-      <c r="O29" s="22" t="inlineStr">
-        <is>
-          <t>https://wccb.com</t>
-        </is>
-      </c>
-      <c r="P29" s="22" t="inlineStr">
-        <is>
-          <t>https://wccb.com/corporate_cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="inlineStr">
-        <is>
-          <t>MONTECITO BANK &amp; TRUST</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>Ventura</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>Santa Barbara</t>
-        </is>
-      </c>
-      <c r="F30" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>NO (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="K30" s="30" t="inlineStr">
-        <is>
-          <t>UNK (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="L30" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN — issuer not confirmed on public pages; uses SpendTr (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M30" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N30" s="22" t="inlineStr">
-        <is>
-          <t>Assisted (appointment/banker)</t>
-        </is>
-      </c>
-      <c r="O30" s="22" t="inlineStr">
-        <is>
-          <t>https://montecito.bank</t>
-        </is>
-      </c>
-      <c r="P30" s="22" t="inlineStr">
-        <is>
-          <t>https://montecito.bank/business/credit-card</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>🟨 2</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="inlineStr">
-        <is>
-          <t>VENTURA COUNTY CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Ventura</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>Ventura</t>
-        </is>
-      </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J31" s="31" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="K31" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L31" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN bureau — VCCU offers business Visa; no membership or (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M31" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N31" s="22" t="inlineStr">
-        <is>
-          <t>Branch/phone</t>
-        </is>
-      </c>
-      <c r="O31" s="22" t="inlineStr">
-        <is>
-          <t>https://www.vccuonline.net</t>
-        </is>
-      </c>
-      <c r="P31" s="22" t="inlineStr">
-        <is>
-          <t>https://www.vccuonline.net/Business</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>🟥 TIER 3 — SCREENS (pulls ChexSystems and/or EWS)</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="33" t="n"/>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="33" t="n"/>
-      <c r="K33" s="33" t="n"/>
-      <c r="L33" s="33" t="n"/>
-      <c r="M33" s="33" t="n"/>
-      <c r="N33" s="33" t="n"/>
-      <c r="O33" s="33" t="n"/>
-      <c r="P33" s="33" t="n"/>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>Bank of America, National Association</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>Charlotte, Long Beach</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I34" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>NO (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K34" s="36" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="L34" s="19" t="inlineStr">
-        <is>
-          <t>EX usual; CA mixed (EX/TU/EQ) — no business-specific upgrade (COMMUNITY-DP-business)</t>
-        </is>
-      </c>
-      <c r="M34" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N34" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O34" s="22" t="inlineStr">
-        <is>
-          <t>https://business.bankofamerica.com</t>
-        </is>
-      </c>
-      <c r="P34" s="22" t="inlineStr">
-        <is>
-          <t>https://business.bankofamerica.com/en/credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B35" s="35" t="inlineStr">
-        <is>
-          <t>Wells Fargo Bank, National Association</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>Sioux Falls, Long Beach, Fontana</t>
-        </is>
-      </c>
-      <c r="F35" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I35" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J35" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K35" s="36" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="L35" s="22" t="inlineStr">
-        <is>
-          <t>Experian dominant for the Signify Business Cash/Business car (B)</t>
-        </is>
-      </c>
-      <c r="M35" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N35" s="22" t="inlineStr">
-        <is>
-          <t>Online (also branch by appt)</t>
-        </is>
-      </c>
-      <c r="O35" s="22" t="inlineStr">
-        <is>
-          <t>https://www.wellsfargo.com</t>
-        </is>
-      </c>
-      <c r="P35" s="22" t="inlineStr">
-        <is>
-          <t>https://www.wellsfargo.com/biz/business-credit/credit-cards/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase Bank, National Association</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>Columbus, Long Beach, Fontana</t>
-        </is>
-      </c>
-      <c r="F36" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I36" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>NO (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K36" s="36" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="L36" s="22" t="inlineStr">
-        <is>
-          <t>Experian dominant in CA (~70%+ of Chase pulls nationally; CA (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="M36" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N36" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O36" s="22" t="inlineStr">
-        <is>
-          <t>https://www.chase.com</t>
-        </is>
-      </c>
-      <c r="P36" s="22" t="inlineStr">
-        <is>
-          <t>https://creditcards.chase.com/business-credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>U.S. Bank National Association</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>Cincinnati, Long Beach, Fontana, Wilmington</t>
-        </is>
-      </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I37" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J37" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K37" s="36" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="L37" s="22" t="inlineStr">
-        <is>
-          <t>TU-usual for business (CA consumer: TU 47%/EX 26%/EQ 5%) (COMMUNITY-DP (business-specific myFICO DPs))</t>
-        </is>
-      </c>
-      <c r="M37" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N37" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O37" s="22" t="inlineStr">
-        <is>
-          <t>https://www.usbank.com</t>
-        </is>
-      </c>
-      <c r="P37" s="22" t="inlineStr">
-        <is>
-          <t>https://www.usbank.com/business-banking/business-credit-cards.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>Citibank, National Association</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; Orange; Ventura; San Diego</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>Sioux Falls, Long Beach, Fontana</t>
-        </is>
-      </c>
-      <c r="F38" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I38" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J38" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K38" s="36" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="L38" s="22" t="inlineStr">
-        <is>
-          <t>Experian primary for Citi AAdvantage Business card; Citi BUS (B)</t>
-        </is>
-      </c>
-      <c r="M38" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N38" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O38" s="22" t="inlineStr">
-        <is>
-          <t>https://www.citi.com</t>
-        </is>
-      </c>
-      <c r="P38" s="22" t="inlineStr">
-        <is>
-          <t>https://www.citi.com/credit-cards/compare/business-credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>Western Alliance Bank</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Diego</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="F39" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H39" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I39" s="22" t="inlineStr">
-        <is>
-          <t>unknown (UNVERIFIED-RUMOR)</t>
-        </is>
-      </c>
-      <c r="J39" s="37" t="inlineStr">
-        <is>
-          <t>YES (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>NO (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="L39" s="22" t="inlineStr">
-        <is>
-          <t>Business Plus Visa card issued DIRECTLY by Western Alliance  (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M39" s="20" t="inlineStr">
-        <is>
-          <t>$1,</t>
-        </is>
-      </c>
-      <c r="N39" s="22" t="inlineStr">
-        <is>
-          <t>Online form -&gt; banker callback in 2-3 business days (not instant online decision)</t>
-        </is>
-      </c>
-      <c r="O39" s="22" t="inlineStr">
-        <is>
-          <t>https://www.westernalliancebancorporation.com</t>
-        </is>
-      </c>
-      <c r="P39" s="22" t="inlineStr">
-        <is>
-          <t>https://www.westernalliancebancorporation.com/small-business/credit-cards/business-plus-credit-card</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>PNC Bank, National Association</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; San Diego</t>
-        </is>
-      </c>
-      <c r="E40" s="19" t="inlineStr">
-        <is>
-          <t>Wilmington</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G40" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I40" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J40" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K40" s="36" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="L40" s="22" t="inlineStr">
-        <is>
-          <t>Experian-leaning for PNC Visa Business per WalletHub + Credi</t>
-        </is>
-      </c>
-      <c r="M40" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N40" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O40" s="22" t="inlineStr">
-        <is>
-          <t>https://www.pnc.com</t>
-        </is>
-      </c>
-      <c r="P40" s="22" t="inlineStr">
-        <is>
-          <t>https://www.pnc.com/en/small-business/borrowing/business-credit-cards/pnc-visa-business-credit-card.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>KINECTA FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Orange; Ventura</t>
-        </is>
-      </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>Manhattan Beach</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G41" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H41" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I41" s="22" t="inlineStr">
-        <is>
-          <t>partial (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J41" s="37" t="inlineStr">
-        <is>
-          <t>YES (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="K41" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L41" s="22" t="inlineStr">
-        <is>
-          <t>No business-card-specific DP; myFICO 'I'm Embarrassed 2nd Pe (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M41" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N41" s="22" t="inlineStr">
-        <is>
-          <t>In-person/phone (book appointment or 800.854.9846; no online app)</t>
-        </is>
-      </c>
-      <c r="O41" s="22" t="inlineStr">
-        <is>
-          <t>https://www.kinecta.org</t>
-        </is>
-      </c>
-      <c r="P41" s="22" t="inlineStr">
-        <is>
-          <t>https://www.kinecta.org/credit-card/mypro</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>NUVISION FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Orange; San Diego</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>Huntington Beac, Carson</t>
-        </is>
-      </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I42" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J42" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K42" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L42" s="22" t="inlineStr">
-        <is>
-          <t>Still unknown. NuVision (Huntington Beach CA; Denali AK divi (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M42" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N42" s="22" t="inlineStr">
-        <is>
-          <t>Online (also fax/branch form)</t>
-        </is>
-      </c>
-      <c r="O42" s="22" t="inlineStr">
-        <is>
-          <t>https://nuvisionfederal.com</t>
-        </is>
-      </c>
-      <c r="P42" s="22" t="inlineStr">
-        <is>
-          <t>https://nuvisionfederal.com/business-banking/credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B43" s="35" t="inlineStr">
-        <is>
-          <t>PROVIDENT CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>San Bernardino; Riverside</t>
-        </is>
-      </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H43" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I43" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J43" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K43" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L43" s="22" t="inlineStr">
-        <is>
-          <t>Hard pull CONFIRMED for cards (SuperMoney); bureau NOT ident (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M43" s="20" t="inlineStr">
-        <is>
-          <t>$1</t>
-        </is>
-      </c>
-      <c r="N43" s="22" t="inlineStr">
-        <is>
-          <t>Online (member flow: new members open biz savings first; existing via online banking)</t>
-        </is>
-      </c>
-      <c r="O43" s="22" t="inlineStr">
-        <is>
-          <t>https://www.providentcu.org</t>
-        </is>
-      </c>
-      <c r="P43" s="22" t="inlineStr">
-        <is>
-          <t>https://www.providentcu.org/business/business-credit-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>Banner Bank</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Riverside; San Diego</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>Walla Walla, Rancho Cucamonga</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H44" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I44" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J44" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K44" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L44" s="22" t="inlineStr">
-        <is>
-          <t>CONFIRMED self-issued: Banner Bank Business Mastercard Credi (VERIFIED-DISCLOSURE)</t>
-        </is>
-      </c>
-      <c r="M44" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N44" s="19" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="O44" s="22" t="inlineStr">
-        <is>
-          <t>https://www.bannerbank.com</t>
-        </is>
-      </c>
-      <c r="P44" s="22" t="inlineStr">
-        <is>
-          <t>https://www.bannerbank.com/business-solutions/services/small-business-credit-card/business-platinum-mastercard</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>ORANGE COUNTY'S FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Bernardino; Orange</t>
-        </is>
-      </c>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t>Santa Ana, Long Beach</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I45" s="22" t="inlineStr">
-        <is>
-          <t>unknown (none-found)</t>
-        </is>
-      </c>
-      <c r="J45" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K45" s="36" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="L45" s="22" t="inlineStr">
-        <is>
-          <t>EXPERIAN - own FAQ/knowledge base states: 'typically pulls a</t>
-        </is>
-      </c>
-      <c r="M45" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N45" s="22" t="inlineStr">
-        <is>
-          <t>Branch/phone (no online business-card app found)</t>
-        </is>
-      </c>
-      <c r="O45" s="22" t="inlineStr">
-        <is>
-          <t>https://www.orangecountyscu.org</t>
-        </is>
-      </c>
-      <c r="P45" s="22" t="inlineStr">
-        <is>
-          <t>https://www.orangecountyscu.org/products/business-services/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>ALTURA FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D46" s="19" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>Riverside</t>
-        </is>
-      </c>
-      <c r="F46" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H46" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I46" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J46" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K46" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L46" s="22" t="inlineStr">
-        <is>
-          <t>No business-card-specific DP. Altura credit-reporting-agenci (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M46" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N46" s="22" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="O46" s="22" t="inlineStr">
-        <is>
-          <t>https://www.alturacu.com</t>
-        </is>
-      </c>
-      <c r="P46" s="22" t="inlineStr">
-        <is>
-          <t>https://www.alturacu.com/business-credit-card/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B47" s="35" t="inlineStr">
-        <is>
-          <t>MidFirst Bank</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Diego</t>
-        </is>
-      </c>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t>Oklahoma City</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H47" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I47" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J47" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K47" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L47" s="22" t="inlineStr">
-        <is>
-          <t>Mixed/any of three — WalletHub answer is consumer-card gener (CONSUMER-PROXY)</t>
-        </is>
-      </c>
-      <c r="M47" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="19" t="inlineStr">
-        <is>
-          <t>In-person (banking center / local banker; no online app shown)</t>
-        </is>
-      </c>
-      <c r="O47" s="22" t="inlineStr">
-        <is>
-          <t>https://www.midfirst.com</t>
-        </is>
-      </c>
-      <c r="P47" s="22" t="inlineStr">
-        <is>
-          <t>https://www.midfirst.com/business-and-commercial/card-solutions/credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B48" s="35" t="inlineStr">
-        <is>
-          <t>Valley National Bank</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E48" s="19" t="inlineStr">
-        <is>
-          <t>Passaic</t>
-        </is>
-      </c>
-      <c r="F48" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G48" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H48" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J48" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K48" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L48" s="22" t="inlineStr">
-        <is>
-          <t>Inquiry bureau still unknown. Confirmed product = Valley Vis (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M48" s="20" t="inlineStr">
-        <is>
-          <t>$25K</t>
-        </is>
-      </c>
-      <c r="N48" s="22" t="inlineStr">
-        <is>
-          <t>Interest form online then rep contact (no direct online app)</t>
-        </is>
-      </c>
-      <c r="O48" s="22" t="inlineStr">
-        <is>
-          <t>https://www.valley.com</t>
-        </is>
-      </c>
-      <c r="P48" s="22" t="inlineStr">
-        <is>
-          <t>https://www.valley.com/business/commercial-lending/valley-visa-business-credit-card</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B49" s="35" t="inlineStr">
-        <is>
-          <t>BAY FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>Redondo Beach</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H49" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J49" s="37" t="inlineStr">
-        <is>
-          <t>YES (VERIFIED-own-doc)</t>
-        </is>
-      </c>
-      <c r="K49" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L49" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN bureau — Business Visa card exists (in-house CU card (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M49" s="20" t="inlineStr">
-        <is>
-          <t>$50K</t>
-        </is>
-      </c>
-      <c r="N49" s="19" t="inlineStr">
-        <is>
-          <t>Contact/branch</t>
-        </is>
-      </c>
-      <c r="O49" s="22" t="inlineStr">
-        <is>
-          <t>https://www.bayfed.com</t>
-        </is>
-      </c>
-      <c r="P49" s="22" t="inlineStr">
-        <is>
-          <t>https://www.bayfed.com/business/visa-credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B50" s="35" t="inlineStr">
-        <is>
-          <t>CHRISTIAN COMMUNITY CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; Orange</t>
-        </is>
-      </c>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>San Dimas</t>
-        </is>
-      </c>
-      <c r="F50" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G50" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H50" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I50" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J50" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K50" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L50" s="22" t="inlineStr">
-        <is>
-          <t>No bureau DP; now operates as AdelFi; business Visa Rewards  (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M50" s="20" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
-      </c>
-      <c r="N50" s="22" t="inlineStr">
-        <is>
-          <t>Contact/assisted ('Contact Us to Apply'; AdelFi membership required first)</t>
-        </is>
-      </c>
-      <c r="O50" s="22" t="inlineStr">
-        <is>
-          <t>https://www.adelfibanking.com</t>
-        </is>
-      </c>
-      <c r="P50" s="22" t="inlineStr">
-        <is>
-          <t>https://www.adelfibanking.com/ministry/ministry-credit-cards/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B51" s="35" t="inlineStr">
-        <is>
-          <t>LOS ANGELES FEDERAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="E51" s="19" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="F51" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H51" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I51" s="22" t="inlineStr">
-        <is>
-          <t>unknown (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="J51" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K51" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L51" s="22" t="inlineStr">
-        <is>
-          <t>TransUnion primary — myFICO DPs: membership hard pull hits T (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="M51" s="20" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="N51" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
       <c r="O51" s="22" t="inlineStr">
         <is>
-          <t>https://www.lafcu.org</t>
+          <t>https://www.sierracentral.com</t>
         </is>
       </c>
       <c r="P51" s="22" t="inlineStr">
         <is>
-          <t>https://www.lafcu.org/loans-credit/business-loans</t>
+          <t>https://www.sierracentral.com/borrow/credit-cards</t>
         </is>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B52" s="35" t="inlineStr">
-        <is>
-          <t>Sunflower Bank, National Association</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>Los Angeles; San Diego</t>
-        </is>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G52" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H52" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>unknown (-)</t>
-        </is>
-      </c>
-      <c r="J52" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K52" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L52" s="22" t="inlineStr">
-        <is>
-          <t>UNKNOWN — Sunflower self-issues business cards (Visa, licens (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M52" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N52" s="22" t="inlineStr">
-        <is>
-          <t>Branch/contact (no online app found)</t>
-        </is>
-      </c>
-      <c r="O52" s="22" t="inlineStr">
-        <is>
-          <t>https://www.sunflowerbank.com</t>
-        </is>
-      </c>
-      <c r="P52" s="22" t="inlineStr">
-        <is>
-          <t>https://www.sunflowerbank.com/business/business-accounts/credit-cards</t>
-        </is>
-      </c>
+      <c r="A52" s="67" t="n"/>
+      <c r="B52" s="44" t="n"/>
+      <c r="C52" s="68" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="19" t="n"/>
+      <c r="J52" s="22" t="n"/>
+      <c r="K52" s="19" t="n"/>
+      <c r="L52" s="22" t="n"/>
+      <c r="M52" s="20" t="n"/>
+      <c r="N52" s="22" t="n"/>
+      <c r="O52" s="22" t="n"/>
+      <c r="P52" s="22" t="n"/>
     </row>
     <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>🟥 3</t>
-        </is>
-      </c>
-      <c r="B53" s="35" t="inlineStr">
-        <is>
-          <t>SIERRA CENTRAL CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>Ventura</t>
-        </is>
-      </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t>Porterville</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H53" s="21" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="I53" s="25" t="inlineStr">
-        <is>
-          <t>⭐ YES (VERIFIED-own-page)</t>
-        </is>
-      </c>
-      <c r="J53" s="37" t="inlineStr">
-        <is>
-          <t>YES (COMMUNITY-DP)</t>
-        </is>
-      </c>
-      <c r="K53" s="30" t="inlineStr">
-        <is>
-          <t>UNK</t>
-        </is>
-      </c>
-      <c r="L53" s="22" t="inlineStr">
-        <is>
-          <t>Still unknown. Sierra Central (Yuba City CA) offers a self-b (UNKNOWN)</t>
-        </is>
-      </c>
-      <c r="M53" s="20" t="inlineStr">
-        <is>
-          <t>$5K</t>
-        </is>
-      </c>
-      <c r="N53" s="22" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="O53" s="22" t="inlineStr">
-        <is>
-          <t>https://www.sierracentral.com</t>
-        </is>
-      </c>
-      <c r="P53" s="22" t="inlineStr">
-        <is>
-          <t>https://www.sierracentral.com/borrow/credit-cards</t>
-        </is>
-      </c>
+      <c r="A53" s="67" t="n"/>
+      <c r="B53" s="44" t="n"/>
+      <c r="C53" s="68" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="20" t="n"/>
+      <c r="H53" s="21" t="n"/>
+      <c r="I53" s="22" t="n"/>
+      <c r="J53" s="22" t="n"/>
+      <c r="K53" s="19" t="n"/>
+      <c r="L53" s="22" t="n"/>
+      <c r="M53" s="20" t="n"/>
+      <c r="N53" s="22" t="n"/>
+      <c r="O53" s="22" t="n"/>
+      <c r="P53" s="22" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P51"/>
+  <mergeCells count="3">
+    <mergeCell ref="A29:P29"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId190"/>
@@ -5147,159 +5257,159 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId352"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10410,7 +10520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B15"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10501,6 +10611,48 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA-2 2026-06-12: City National 🟩1→🟨2 (Chex twin-ambiguous CNB-WV; crediful says uses Chex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA-2: Beneficial State 🟩1→🟨2 (Chex/EWS = own-doc absence only, not confirmed NO); card link 403 fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA-2: America's Christian CU 🟨2→🟥3 (uses ChexSystems, lenient=YES per rule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA-2: First-Citizens Chex NO→YES, 🟨2→🟥3 (source confirms uses ChexSystems)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA-2: Commercial Bank of California stays 🟩1 but marked DEPOSIT-ONLY (no card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RESULT: Tier1=1 (CBC, deposit-only) / Tier2=24 / Tier3=22. No card-bearing bank meets strict bar.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
